--- a/Assets/Excels/WaveData.xlsx
+++ b/Assets/Excels/WaveData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>stagenum</t>
   </si>
@@ -62,6 +62,10 @@
   <si>
     <t>SubStagenum</t>
   </si>
+  <si>
+    <t>StageNum</t>
+  </si>
+  <si/>
 </sst>
 </file>
 
@@ -1064,7 +1068,8 @@
     <col min="5" max="5" style="1" width="12.75500011" customWidth="1" outlineLevel="0"/>
     <col min="6" max="7" style="1" width="12.13000011" customWidth="1" outlineLevel="0"/>
     <col min="8" max="8" style="1" width="15.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="16383" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="16384" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1">

--- a/Assets/Excels/WaveData.xlsx
+++ b/Assets/Excels/WaveData.xlsx
@@ -1058,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="5.50500011" customWidth="1" outlineLevel="0"/>
@@ -1068,8 +1068,7 @@
     <col min="5" max="5" style="1" width="12.75500011" customWidth="1" outlineLevel="0"/>
     <col min="6" max="7" style="1" width="12.13000011" customWidth="1" outlineLevel="0"/>
     <col min="8" max="8" style="1" width="15.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="16383" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="16384" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1">
@@ -1158,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -1181,7 +1180,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -1233,13 +1232,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -1259,13 +1258,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1314,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1337,10 +1336,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
@@ -1392,10 +1391,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1415,13 +1414,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -1470,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -1493,10 +1492,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -1548,10 +1547,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
@@ -1571,13 +1570,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -1626,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -1649,10 +1648,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -1704,10 +1703,10 @@
         <v>2</v>
       </c>
       <c r="C25" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -1727,13 +1726,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -1782,7 +1781,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -1805,10 +1804,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -1860,10 +1859,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -1883,13 +1882,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -1938,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -1961,10 +1960,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -2016,10 +2015,10 @@
         <v>2</v>
       </c>
       <c r="C37" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
@@ -2031,32 +2030,6 @@
         <v>2</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="1">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1">
-        <v>2</v>
-      </c>
-      <c r="C38" s="1">
-        <v>24</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2</v>
-      </c>
-      <c r="H38" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/WaveData.xlsx
+++ b/Assets/Excels/WaveData.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
   </bookViews>
   <sheets>
     <sheet name="WaveData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors/>
-  <commentList/>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>stagenum</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>int</t>
   </si>
@@ -56,357 +50,69 @@
   <si>
     <t>ID</t>
   </si>
-  <si>
-    <t>Substagenum</t>
-  </si>
-  <si>
-    <t>SubStagenum</t>
-  </si>
-  <si>
-    <t>StageNum</t>
-  </si>
-  <si/>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="10"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="11"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFF0000"/>
-    </font>
-    <font>
-      <sz val="18.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F76"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F3F"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C0006"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C6500"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -421,252 +127,17 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399980"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -677,67 +148,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
-    <cellStyle name="경고문" xfId="9" builtinId="11"/>
-    <cellStyle name="계산" xfId="17" builtinId="22"/>
-    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
-    <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="5" builtinId="5"/>
-    <cellStyle name="보통" xfId="23" builtinId="28"/>
-    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
-    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+  <cellStyles count="3">
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="요약" xfId="20" builtinId="25"/>
-    <cellStyle name="입력" xfId="15" builtinId="20"/>
-    <cellStyle name="제목" xfId="10" builtinId="15"/>
-    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
-    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
-    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
-    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
-    <cellStyle name="좋음" xfId="21" builtinId="26"/>
-    <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="4" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1057,73 +492,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" style="1" width="5.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" style="1" width="5.75500011" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="3" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" style="1" width="6.38000011" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" style="1" width="12.75500011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="7" style="1" width="12.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" style="1" width="15.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" width="5.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.09765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.09765625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1134,91 +570,91 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
@@ -1227,12 +663,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -1244,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1264,91 +700,91 @@
         <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
+        <v>6</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
         <v>3</v>
       </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
       <c r="C10" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1">
         <v>7</v>
       </c>
       <c r="D11" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1357,128 +793,128 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
         <v>2</v>
@@ -1487,59 +923,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1547,68 +983,68 @@
         <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G21" s="1">
         <v>2</v>
@@ -1617,59 +1053,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1677,68 +1113,68 @@
         <v>2</v>
       </c>
       <c r="C24" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G25" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1">
         <v>2</v>
@@ -1747,33 +1183,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1781,25 +1217,25 @@
         <v>1</v>
       </c>
       <c r="C28" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1807,68 +1243,68 @@
         <v>2</v>
       </c>
       <c r="C29" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D29" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G29" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D30" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G30" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -1877,166 +1313,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1">
-        <v>21</v>
-      </c>
-      <c r="D33" s="1">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1">
-        <v>22</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34" s="1">
-        <v>2</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="1">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2</v>
-      </c>
-      <c r="C35" s="1">
-        <v>23</v>
-      </c>
-      <c r="D35" s="1">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="1">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1">
-        <v>23</v>
-      </c>
-      <c r="D36" s="1">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1">
-        <v>0</v>
-      </c>
-      <c r="F36" s="1">
-        <v>2</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="1">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1">
-        <v>2</v>
-      </c>
-      <c r="C37" s="1">
-        <v>24</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
-        <v>2</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2</v>
-      </c>
-      <c r="H37" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excels/WaveData.xlsx
+++ b/Assets/Excels/WaveData.xlsx
@@ -820,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E8" s="9">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E9" s="9">
         <v>0</v>
@@ -924,13 +924,13 @@
         <v>10</v>
       </c>
       <c r="D12" s="9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12" s="9">
         <v>0</v>
       </c>
       <c r="F12" s="9">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
@@ -950,13 +950,13 @@
         <v>11</v>
       </c>
       <c r="D13" s="9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E13" s="9">
         <v>0</v>
       </c>
       <c r="F13" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="9">
         <v>3</v>
@@ -1028,13 +1028,13 @@
         <v>14</v>
       </c>
       <c r="D16" s="9">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E16" s="9">
         <v>0</v>
       </c>
       <c r="F16" s="9">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="9">
         <v>3</v>
@@ -1054,13 +1054,13 @@
         <v>15</v>
       </c>
       <c r="D17" s="9">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E17" s="9">
         <v>0</v>
       </c>
       <c r="F17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="9">
         <v>3</v>
@@ -1132,13 +1132,13 @@
         <v>18</v>
       </c>
       <c r="D20" s="9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E20" s="9">
         <v>0</v>
       </c>
       <c r="F20" s="9">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="G20" s="9">
         <v>3</v>
@@ -1158,13 +1158,13 @@
         <v>19</v>
       </c>
       <c r="D21" s="9">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E21" s="9">
         <v>0</v>
       </c>
       <c r="F21" s="9">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="G21" s="9">
         <v>3</v>
@@ -1236,13 +1236,13 @@
         <v>22</v>
       </c>
       <c r="D24" s="9">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E24" s="9">
         <v>0</v>
       </c>
       <c r="F24" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="9">
         <v>3</v>
@@ -1262,13 +1262,13 @@
         <v>23</v>
       </c>
       <c r="D25" s="9">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E25" s="9">
         <v>0</v>
       </c>
       <c r="F25" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="9">
         <v>3</v>

--- a/Assets/Excels/WaveData.xlsx
+++ b/Assets/Excels/WaveData.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5352D731-D517-4B81-82A9-BACECA663AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WaveData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -54,8 +68,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +106,14 @@
       <u/>
       <sz val="11"/>
       <color theme="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -262,9 +284,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -275,6 +294,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -612,22 +634,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.796875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.09765625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -653,7 +675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -679,7 +701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -705,85 +727,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="1">
         <v>15</v>
       </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
-        <v>3</v>
-      </c>
-      <c r="G4" s="9">
-        <v>3</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="9">
-        <v>3</v>
-      </c>
-      <c r="C5" s="9">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
         <v>15</v>
       </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9">
-        <v>3</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="11">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>4</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0</v>
-      </c>
-      <c r="G6" s="12">
-        <v>3</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
+        <v>3</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -809,85 +833,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>6</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="1">
         <v>2</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="1">
         <v>6</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="1">
         <v>25</v>
       </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
-        <v>3</v>
-      </c>
-      <c r="G8" s="9">
-        <v>3</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="9">
-        <v>3</v>
-      </c>
-      <c r="C9" s="9">
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
         <v>7</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="1">
         <v>30</v>
       </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="9">
-        <v>3</v>
-      </c>
-      <c r="G9" s="9">
-        <v>3</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11">
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>4</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>8</v>
       </c>
-      <c r="D10" s="12">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>3</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D10" s="11">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>3</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -913,85 +937,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>10</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="1">
         <v>10</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="1">
         <v>28</v>
       </c>
-      <c r="E12" s="9">
-        <v>0</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
         <v>2.5</v>
       </c>
-      <c r="G12" s="9">
-        <v>3</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>11</v>
       </c>
-      <c r="B13" s="9">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9">
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
         <v>11</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="1">
         <v>35</v>
       </c>
-      <c r="E13" s="9">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="9">
-        <v>3</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11">
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>4</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>12</v>
       </c>
-      <c r="D14" s="12">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12">
-        <v>0</v>
-      </c>
-      <c r="F14" s="12">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>3</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D14" s="11">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11">
+        <v>3</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -1017,85 +1041,86 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>14</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="1">
         <v>2</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="1">
         <v>14</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="1">
         <v>32</v>
       </c>
-      <c r="E16" s="9">
-        <v>0</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
         <v>2.5</v>
       </c>
-      <c r="G16" s="9">
-        <v>3</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>15</v>
       </c>
-      <c r="B17" s="9">
-        <v>3</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1">
         <v>15</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="1">
         <v>40</v>
       </c>
-      <c r="E17" s="9">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9">
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="9">
-        <v>3</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="11">
+      <c r="G17" s="1">
+        <v>3</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
         <v>16</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>16</v>
       </c>
-      <c r="D18" s="12">
-        <v>1</v>
-      </c>
-      <c r="E18" s="12">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12">
-        <v>0</v>
-      </c>
-      <c r="G18" s="12">
-        <v>3</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11">
+        <v>3</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -1121,85 +1146,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>18</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="1">
         <v>2</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="1">
         <v>18</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="1">
         <v>37</v>
       </c>
-      <c r="E20" s="9">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
         <v>2.25</v>
       </c>
-      <c r="G20" s="9">
-        <v>3</v>
-      </c>
-      <c r="H20" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>19</v>
       </c>
-      <c r="B21" s="9">
-        <v>3</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
         <v>19</v>
       </c>
-      <c r="D21" s="9">
-        <v>45</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
+      <c r="D21" s="1">
+        <v>50</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
         <v>1.75</v>
       </c>
-      <c r="G21" s="9">
-        <v>3</v>
-      </c>
-      <c r="H21" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="11">
+      <c r="G21" s="1">
+        <v>3</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
         <v>20</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>4</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <v>20</v>
       </c>
-      <c r="D22" s="12">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12">
-        <v>0</v>
-      </c>
-      <c r="F22" s="12">
-        <v>0</v>
-      </c>
-      <c r="G22" s="12">
-        <v>3</v>
-      </c>
-      <c r="H22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <v>3</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>21</v>
       </c>
@@ -1225,83 +1250,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>22</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="1">
         <v>22</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="1">
         <v>42</v>
       </c>
-      <c r="E24" s="9">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
         <v>2</v>
       </c>
-      <c r="G24" s="9">
-        <v>3</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G24" s="1">
+        <v>3</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>23</v>
       </c>
-      <c r="B25" s="9">
-        <v>3</v>
-      </c>
-      <c r="C25" s="9">
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
         <v>23</v>
       </c>
-      <c r="D25" s="9">
-        <v>50</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9">
-        <v>1</v>
-      </c>
-      <c r="G25" s="9">
-        <v>3</v>
-      </c>
-      <c r="H25" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="11">
+      <c r="D25" s="1">
+        <v>60</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
         <v>24</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>4</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <v>24</v>
       </c>
-      <c r="D26" s="12">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12">
-        <v>0</v>
-      </c>
-      <c r="F26" s="12">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12">
-        <v>3</v>
-      </c>
-      <c r="H26" s="13">
-        <v>0</v>
-      </c>
+      <c r="D26" s="11">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11">
+        <v>3</v>
+      </c>
+      <c r="H26" s="12">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Excels/WaveData.xlsx
+++ b/Assets/Excels/WaveData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5352D731-D517-4B81-82A9-BACECA663AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A1B9CA-0CE9-4611-8FCA-311036C7F8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WaveData" sheetId="1" r:id="rId1"/>
@@ -256,7 +256,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -297,6 +297,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -646,7 +649,8 @@
     <col min="6" max="7" width="12.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -712,7 +716,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E3" s="6">
         <v>0</v>
@@ -738,13 +742,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -752,6 +756,7 @@
       <c r="H4" s="9">
         <v>0</v>
       </c>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
@@ -764,13 +769,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -778,7 +783,7 @@
       <c r="H5" s="9">
         <v>0</v>
       </c>
-      <c r="J5" s="13"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
@@ -844,13 +849,13 @@
         <v>6</v>
       </c>
       <c r="D8" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -858,6 +863,7 @@
       <c r="H8" s="9">
         <v>0</v>
       </c>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
@@ -870,13 +876,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
         <v>3</v>
@@ -884,6 +890,7 @@
       <c r="H9" s="9">
         <v>0</v>
       </c>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
@@ -948,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="D12" s="1">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="G12" s="1">
         <v>3</v>
@@ -962,6 +969,7 @@
       <c r="H12" s="9">
         <v>0</v>
       </c>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
@@ -974,13 +982,13 @@
         <v>11</v>
       </c>
       <c r="D13" s="1">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -988,6 +996,7 @@
       <c r="H13" s="9">
         <v>0</v>
       </c>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
@@ -1052,13 +1061,13 @@
         <v>14</v>
       </c>
       <c r="D16" s="1">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -1067,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>15</v>
       </c>
@@ -1078,13 +1087,13 @@
         <v>15</v>
       </c>
       <c r="D17" s="1">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -1092,9 +1101,9 @@
       <c r="H17" s="9">
         <v>0</v>
       </c>
-      <c r="I17" s="13"/>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>16</v>
       </c>
@@ -1120,7 +1129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -1146,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>18</v>
       </c>
@@ -1157,13 +1166,13 @@
         <v>18</v>
       </c>
       <c r="D20" s="1">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
@@ -1172,7 +1181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>19</v>
       </c>
@@ -1183,13 +1192,13 @@
         <v>19</v>
       </c>
       <c r="D21" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>1.75</v>
+        <v>0.95</v>
       </c>
       <c r="G21" s="1">
         <v>3</v>
@@ -1197,8 +1206,9 @@
       <c r="H21" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>20</v>
       </c>
@@ -1224,7 +1234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>21</v>
       </c>
@@ -1250,7 +1260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>22</v>
       </c>
@@ -1261,13 +1271,13 @@
         <v>22</v>
       </c>
       <c r="D24" s="1">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -1276,7 +1286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>23</v>
       </c>
@@ -1287,13 +1297,13 @@
         <v>23</v>
       </c>
       <c r="D25" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G25" s="1">
         <v>3</v>
@@ -1301,8 +1311,9 @@
       <c r="H25" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>24</v>
       </c>
@@ -1327,7 +1338,6 @@
       <c r="H26" s="12">
         <v>0</v>
       </c>
-      <c r="I26" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
